--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -425,21 +422,21 @@
     <t>Encounter.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -449,31 +446,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:next-visit</t>
-  </si>
-  <si>
-    <t>next-visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-care-next-visit}
-</t>
-  </si>
-  <si>
-    <t>Next Appointment Date</t>
-  </si>
-  <si>
-    <t>A date representing the patient's next scheduled appointment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Encounter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -483,9 +456,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -586,9 +556,6 @@
   </si>
   <si>
     <t>Encounter.statusHistory.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1606,21 +1573,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1794,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN75"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -1807,7 +1759,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.4296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.65625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1960,7 +1912,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2072,7 +2024,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2186,7 +2138,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2298,7 +2250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2412,7 +2364,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2526,7 +2478,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2640,7 +2592,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2754,7 +2706,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2763,7 +2715,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2782,15 +2734,17 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2827,14 +2781,16 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>137</v>
@@ -2855,7 +2811,7 @@
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -2864,46 +2820,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I10" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2951,7 +2909,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2960,7 +2918,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>138</v>
@@ -2969,7 +2927,7 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -2978,16 +2936,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3000,26 +2958,22 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
       </c>
@@ -3067,7 +3021,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3079,22 +3033,22 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
@@ -3107,30 +3061,32 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3155,13 +3111,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3182,10 +3138,10 @@
         <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>80</v>
@@ -3194,24 +3150,24 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3219,31 +3175,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3269,13 +3225,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3293,13 +3249,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3308,24 +3264,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3336,7 +3292,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
@@ -3348,17 +3304,15 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3407,25 +3361,25 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3434,23 +3388,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
@@ -3462,15 +3416,17 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3519,25 +3475,25 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3546,16 +3502,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3568,24 +3524,26 @@
         <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3633,7 +3591,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3651,7 +3609,7 @@
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3660,48 +3618,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3725,13 +3679,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3749,25 +3703,25 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -3776,12 +3730,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3804,13 +3758,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3837,13 +3791,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3861,7 +3815,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>87</v>
@@ -3879,7 +3833,7 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -3888,12 +3842,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3913,16 +3867,16 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3949,13 +3903,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -3973,7 +3927,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>87</v>
@@ -3991,21 +3945,21 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4013,10 +3967,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4025,10 +3979,10 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>198</v>
@@ -4061,13 +4015,13 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>80</v>
@@ -4085,13 +4039,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4103,21 +4057,21 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4128,7 +4082,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -4140,13 +4094,13 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4197,25 +4151,25 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4224,23 +4178,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4252,15 +4206,17 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4309,25 +4265,25 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
@@ -4336,16 +4292,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4358,24 +4314,26 @@
         <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4423,7 +4381,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4441,7 +4399,7 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
@@ -4450,48 +4408,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4515,13 +4469,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4539,25 +4493,25 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4566,12 +4520,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4594,13 +4548,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4627,13 +4581,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -4651,7 +4605,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>87</v>
@@ -4669,7 +4623,7 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4678,12 +4632,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4691,10 +4645,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4703,18 +4657,20 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4739,13 +4695,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4763,13 +4719,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -4778,24 +4734,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4806,7 +4762,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4818,17 +4774,15 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N27" t="s" s="2">
         <v>222</v>
       </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4853,14 +4807,14 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4877,13 +4831,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -4892,24 +4846,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4929,16 +4883,16 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4965,13 +4919,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -4989,7 +4943,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5004,32 +4958,32 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
@@ -5041,10 +4995,10 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>236</v>
@@ -5052,7 +5006,9 @@
       <c r="M29" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5077,13 +5033,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5101,7 +5057,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5116,35 +5072,35 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5164,9 +5120,7 @@
       <c r="M30" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5215,13 +5169,13 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
@@ -5230,32 +5184,32 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AM30" t="s" s="2">
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AN30" t="s" s="2">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -5267,16 +5221,16 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5327,7 +5281,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5342,28 +5296,28 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AM31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5379,16 +5333,16 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>261</v>
+        <v>164</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,7 +5393,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5454,24 +5408,24 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5482,7 +5436,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5491,16 +5445,16 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5551,50 +5505,50 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>270</v>
+        <v>168</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5606,15 +5560,17 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5663,25 +5619,25 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -5690,16 +5646,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5712,24 +5668,26 @@
         <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5777,7 +5735,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5795,7 +5753,7 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
@@ -5804,16 +5762,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5826,26 +5784,24 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5869,13 +5825,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5893,7 +5849,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5905,27 +5861,27 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5936,7 +5892,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -5945,20 +5901,18 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5983,13 +5937,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6007,13 +5961,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -6022,24 +5976,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6059,16 +6013,16 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6119,7 +6073,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6134,24 +6088,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN38" t="s" s="2">
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
         <v>287</v>
       </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6162,7 +6116,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6174,13 +6128,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6231,13 +6185,13 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
@@ -6246,24 +6200,24 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL39" t="s" s="2">
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6271,10 +6225,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6283,18 +6237,20 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>297</v>
+        <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6343,13 +6299,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6358,24 +6314,24 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>301</v>
       </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6383,7 +6339,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>87</v>
@@ -6398,7 +6354,7 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>303</v>
@@ -6457,7 +6413,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6472,35 +6428,35 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AM41" t="s" s="2">
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6509,19 +6465,19 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6547,13 +6503,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6571,13 +6527,13 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
@@ -6586,28 +6542,28 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6626,16 +6582,16 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6661,13 +6617,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -6685,7 +6641,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6700,28 +6656,28 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6740,17 +6696,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>329</v>
+        <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6799,7 +6753,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6814,24 +6768,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>325</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6842,7 +6796,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6851,16 +6805,16 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6911,25 +6865,25 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>173</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>334</v>
+        <v>168</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -6938,23 +6892,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -6966,15 +6920,17 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7023,25 +6979,25 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7050,16 +7006,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7072,24 +7028,26 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7137,7 +7095,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7155,7 +7113,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7164,48 +7122,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>188</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>189</v>
+        <v>333</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7253,47 +7209,47 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>87</v>
@@ -7305,20 +7261,18 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7343,13 +7297,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7367,10 +7321,10 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>87</v>
@@ -7382,24 +7336,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7422,13 +7376,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7455,13 +7409,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7479,7 +7433,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7497,7 +7451,7 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>176</v>
+        <v>346</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
@@ -7506,12 +7460,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7522,7 +7476,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7534,15 +7488,17 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7591,13 +7547,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7609,7 +7565,7 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7618,12 +7574,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7634,7 +7590,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7646,16 +7602,16 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7705,13 +7661,13 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
@@ -7723,7 +7679,7 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -7732,12 +7688,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7760,17 +7716,15 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7819,7 +7773,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>173</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7831,13 +7785,13 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>366</v>
+        <v>168</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -7846,23 +7800,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -7874,15 +7828,17 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -7931,25 +7887,25 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -7958,16 +7914,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7980,24 +7936,26 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8045,7 +8003,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8063,7 +8021,7 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8072,48 +8030,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>188</v>
+        <v>362</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8161,39 +8115,39 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>190</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8216,13 +8170,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>153</v>
+        <v>366</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8273,7 +8227,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8291,21 +8245,21 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>157</v>
+        <v>369</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8328,13 +8282,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>375</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8361,13 +8315,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8385,7 +8339,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8403,21 +8357,21 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8440,13 +8394,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8473,13 +8427,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8497,7 +8451,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8515,21 +8469,21 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>384</v>
+        <v>168</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8540,7 +8494,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -8552,16 +8506,20 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8585,14 +8543,14 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8609,13 +8567,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -8627,7 +8585,7 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>176</v>
+        <v>390</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -8636,7 +8594,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>392</v>
       </c>
@@ -8664,7 +8622,7 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>393</v>
@@ -8672,12 +8630,8 @@
       <c r="M61" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>396</v>
-      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8701,13 +8655,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -8743,21 +8697,21 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,13 +8734,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8816,10 +8770,10 @@
         <v>111</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -8837,7 +8791,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8855,21 +8809,21 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8880,7 +8834,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -8892,13 +8846,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>219</v>
+        <v>366</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8925,13 +8879,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -8949,13 +8903,13 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
@@ -8967,21 +8921,21 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9004,13 +8958,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>375</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9037,13 +8991,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9061,7 +9015,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9079,21 +9033,21 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9104,7 +9058,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9116,15 +9070,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9149,13 +9105,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9173,13 +9129,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9191,21 +9147,21 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9216,7 +9172,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -9228,17 +9184,15 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L66" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>430</v>
-      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9287,25 +9241,25 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>173</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>431</v>
+        <v>168</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9314,23 +9268,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -9342,15 +9296,17 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -9399,25 +9355,25 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -9426,16 +9382,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9448,24 +9404,26 @@
         <v>80</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -9513,7 +9471,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9531,7 +9489,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -9540,48 +9498,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>427</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>188</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
@@ -9629,39 +9583,39 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>190</v>
+        <v>426</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>130</v>
+        <v>284</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9669,7 +9623,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
@@ -9684,15 +9638,17 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L70" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -9717,13 +9673,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -9741,10 +9697,10 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>87</v>
@@ -9756,24 +9712,24 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN70" t="s" s="2">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="B71" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9796,16 +9752,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9831,13 +9787,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -9855,7 +9811,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9873,7 +9829,7 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
@@ -9882,12 +9838,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9910,17 +9866,15 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -9945,13 +9899,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>453</v>
+        <v>80</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -9969,7 +9923,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9987,7 +9941,7 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -9996,12 +9950,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10024,13 +9978,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>193</v>
+        <v>450</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10081,7 +10035,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10096,24 +10050,24 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>286</v>
+        <v>453</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>80</v>
+        <v>454</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10136,15 +10090,17 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10193,7 +10149,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10208,151 +10164,19 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>292</v>
+        <v>460</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN75" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN75">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-target-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
